--- a/output/graficos_regionales_cobertura/plot_comunal_cobertura_2023_antofagasta.xlsx
+++ b/output/graficos_regionales_cobertura/plot_comunal_cobertura_2023_antofagasta.xlsx
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-08 13:48</t>
+    <t xml:space="preserve">2026-09-09 20:11</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_cobertura/plot_comunal_cobertura_2023_antofagasta.xlsx
+++ b/output/graficos_regionales_cobertura/plot_comunal_cobertura_2023_antofagasta.xlsx
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 20:11</t>
+    <t xml:space="preserve">2026-09-18 17:06</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_cobertura/plot_comunal_cobertura_2023_antofagasta.xlsx
+++ b/output/graficos_regionales_cobertura/plot_comunal_cobertura_2023_antofagasta.xlsx
@@ -30,33 +30,33 @@
     <t xml:space="preserve">Cobertura</t>
   </si>
   <si>
+    <t xml:space="preserve">Mejillones</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Pedro de Atacama</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taltal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tocopilla</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calama</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Antofagasta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sierra Gorda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">María Elena</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ollagüe</t>
   </si>
   <si>
-    <t xml:space="preserve">María Elena</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sierra Gorda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Antofagasta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calama</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tocopilla</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taltal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Pedro de Atacama</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mejillones</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 17:06</t>
+    <t xml:space="preserve">2026-09-27 21:52</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -486,13 +486,13 @@
         <v>4</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>193</v>
+        <v>16995</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>274</v>
+        <v>15659</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>70.44</v>
+        <v>108.53</v>
       </c>
     </row>
     <row r="3">
@@ -500,13 +500,13 @@
         <v>5</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>4920</v>
+        <v>10932</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>6592</v>
+        <v>10929</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>74.64</v>
+        <v>100.03</v>
       </c>
     </row>
     <row r="4">
@@ -514,13 +514,13 @@
         <v>6</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>1430</v>
+        <v>13346</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>1792</v>
+        <v>13929</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>79.8</v>
+        <v>95.81</v>
       </c>
     </row>
     <row r="5">
@@ -528,13 +528,13 @@
         <v>7</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>402287</v>
+        <v>26963</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>441211</v>
+        <v>28333</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>91.18</v>
+        <v>95.16</v>
       </c>
     </row>
     <row r="6">
@@ -556,13 +556,13 @@
         <v>9</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>26963</v>
+        <v>402287</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>28333</v>
+        <v>441211</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>95.16</v>
+        <v>91.18</v>
       </c>
     </row>
     <row r="8">
@@ -570,13 +570,13 @@
         <v>10</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>13346</v>
+        <v>1430</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>13929</v>
+        <v>1792</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>95.81</v>
+        <v>79.8</v>
       </c>
     </row>
     <row r="9">
@@ -584,13 +584,13 @@
         <v>11</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>10932</v>
+        <v>4920</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>10929</v>
+        <v>6592</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>100.03</v>
+        <v>74.64</v>
       </c>
     </row>
     <row r="10">
@@ -598,13 +598,13 @@
         <v>12</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>16995</v>
+        <v>193</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>15659</v>
+        <v>274</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>108.53</v>
+        <v>70.44</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_regionales_cobertura/plot_comunal_cobertura_2023_antofagasta.xlsx
+++ b/output/graficos_regionales_cobertura/plot_comunal_cobertura_2023_antofagasta.xlsx
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 21:52</t>
+    <t xml:space="preserve">2026-10-05 05:49</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
